--- a/resources/data-imports/Monsters/labyrinth-celestials.xlsx
+++ b/resources/data-imports/Monsters/labyrinth-celestials.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -327,20 +327,24 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -364,34 +368,34 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -537,1188 +541,1188 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AX11"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="13.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="15.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="15.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="19.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="15.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="18.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="17.39"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="0" width="21.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="0" width="24.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="27" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="31" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="32" style="0" width="19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="33" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="34" style="0" width="27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="35" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="0" width="19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="38" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="39" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="40" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="41" min="41" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="43" min="42" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="44" min="44" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="46" min="45" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="47" min="47" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="49" min="48" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="50" min="50" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="13.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="12.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="13.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="13.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="15.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="15.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="19.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="15.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="18.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="17.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="1" width="21.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="1" width="24.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="27" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="31" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="32" style="1" width="19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="33" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="34" style="1" width="27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="35" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="1" width="19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="38" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="39" style="1" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="40" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="41" min="41" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="43" min="42" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="44" min="44" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="46" min="45" style="1" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="47" min="47" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="49" min="48" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="50" min="50" style="1" width="24"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AA1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AB1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AC1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AD1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AE1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AF1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AG1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AH1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AI1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AJ1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AK1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AL1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AM1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AN1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AO1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AP1" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AQ1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AR1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AS1" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AT1" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AU1" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AV1" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="AW1" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="AX1" s="2" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="C2" s="1" t="n">
         <v>31473125</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="1" t="n">
         <v>31473125</v>
       </c>
-      <c r="E2" s="0" t="n">
+      <c r="E2" s="1" t="n">
         <v>31473125</v>
       </c>
-      <c r="F2" s="0" t="n">
+      <c r="F2" s="1" t="n">
         <v>31473125</v>
       </c>
-      <c r="G2" s="0" t="n">
+      <c r="G2" s="1" t="n">
         <v>31473125</v>
       </c>
-      <c r="H2" s="0" t="n">
+      <c r="H2" s="1" t="n">
         <v>31473125</v>
       </c>
-      <c r="I2" s="0" t="n">
+      <c r="I2" s="1" t="n">
         <v>31473125</v>
       </c>
-      <c r="J2" s="0" t="n">
+      <c r="J2" s="1" t="n">
         <v>31473125</v>
       </c>
-      <c r="K2" s="0" t="n">
+      <c r="K2" s="1" t="n">
         <v>0.18133515</v>
       </c>
-      <c r="L2" s="0" t="n">
+      <c r="L2" s="1" t="n">
         <v>0.18133515</v>
       </c>
-      <c r="M2" s="0" t="n">
+      <c r="M2" s="1" t="n">
         <v>0.18133515</v>
       </c>
-      <c r="N2" s="0" t="n">
+      <c r="N2" s="1" t="n">
         <v>0.18133515</v>
       </c>
-      <c r="O2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P2" s="2" t="n">
+      <c r="O2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" s="3" t="n">
         <v>5747.937</v>
       </c>
-      <c r="Q2" s="2" t="n">
+      <c r="Q2" s="3" t="n">
         <v>478.597</v>
       </c>
-      <c r="R2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="S2" s="0" t="n">
+      <c r="R2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T2" s="0" t="s">
+      <c r="T2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="U2" s="2" t="n">
+      <c r="U2" s="3" t="n">
         <v>52.238925</v>
       </c>
-      <c r="V2" s="0" t="n">
+      <c r="V2" s="1" t="n">
         <v>0.1205844</v>
       </c>
-      <c r="W2" s="0" t="n">
-        <v>293654500</v>
-      </c>
-      <c r="X2" s="2" t="n">
+      <c r="W2" s="1" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="X2" s="3" t="n">
         <v>101.19621</v>
       </c>
-      <c r="Y2" s="0" t="s">
+      <c r="Y2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="Z2" s="0" t="s">
+      <c r="Z2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="AA2" s="0" t="n">
+      <c r="AA2" s="1" t="n">
         <v>31473125</v>
       </c>
-      <c r="AB2" s="0" t="n">
+      <c r="AB2" s="1" t="n">
         <v>31473125</v>
       </c>
-      <c r="AC2" s="0" t="n">
+      <c r="AC2" s="1" t="n">
         <v>0.18133515</v>
       </c>
-      <c r="AD2" s="0" t="n">
+      <c r="AD2" s="1" t="n">
         <v>0.18133515</v>
       </c>
-      <c r="AE2" s="0" t="n">
+      <c r="AE2" s="1" t="n">
         <v>0.18133515</v>
       </c>
-      <c r="AF2" s="0" t="n">
+      <c r="AF2" s="1" t="n">
         <v>0.18133515</v>
       </c>
-      <c r="AO2" s="3" t="s">
+      <c r="AO2" s="4" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C3" s="3" t="n">
         <v>39622303.890625</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="3" t="n">
         <v>39622303.890625</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="3" t="n">
         <v>39622303.890625</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="3" t="n">
         <v>39622303.890625</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="G3" s="3" t="n">
         <v>39622303.890625</v>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="H3" s="3" t="n">
         <v>39622303.890625</v>
       </c>
-      <c r="I3" s="2" t="n">
+      <c r="I3" s="3" t="n">
         <v>39622303.890625</v>
       </c>
-      <c r="J3" s="2" t="n">
+      <c r="J3" s="3" t="n">
         <v>39622303.890625</v>
       </c>
-      <c r="K3" s="0" t="n">
+      <c r="K3" s="1" t="n">
         <v>0.21921624417015</v>
       </c>
-      <c r="L3" s="0" t="n">
+      <c r="L3" s="1" t="n">
         <v>0.21921624417015</v>
       </c>
-      <c r="M3" s="0" t="n">
+      <c r="M3" s="1" t="n">
         <v>0.21921624417015</v>
       </c>
-      <c r="N3" s="0" t="n">
+      <c r="N3" s="1" t="n">
         <v>0.21921624417015</v>
       </c>
-      <c r="O3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P3" s="2" t="n">
+      <c r="O3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" s="3" t="n">
         <v>11012.926585323</v>
       </c>
-      <c r="Q3" s="2" t="n">
+      <c r="Q3" s="3" t="n">
         <v>654.44310974</v>
       </c>
-      <c r="R3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="S3" s="0" t="n">
+      <c r="R3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T3" s="0" t="s">
+      <c r="T3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="U3" s="2" t="n">
+      <c r="U3" s="3" t="n">
         <v>60.642339670125</v>
       </c>
-      <c r="V3" s="0" t="n">
+      <c r="V3" s="1" t="n">
         <v>0.1454059752336</v>
       </c>
-      <c r="W3" s="2" t="n">
-        <v>344931861.481</v>
-      </c>
-      <c r="X3" s="2" t="n">
+      <c r="W3" s="3" t="n">
+        <v>1429969</v>
+      </c>
+      <c r="X3" s="3" t="n">
         <v>136.542305578188</v>
       </c>
-      <c r="Y3" s="0" t="s">
+      <c r="Y3" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="Z3" s="0" t="s">
+      <c r="Z3" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="AA3" s="2" t="n">
+      <c r="AA3" s="3" t="n">
         <v>39622303.890625</v>
       </c>
-      <c r="AB3" s="2" t="n">
+      <c r="AB3" s="3" t="n">
         <v>39622303.890625</v>
       </c>
-      <c r="AC3" s="0" t="n">
+      <c r="AC3" s="1" t="n">
         <v>0.21921624417015</v>
       </c>
-      <c r="AD3" s="0" t="n">
+      <c r="AD3" s="1" t="n">
         <v>0.21921624417015</v>
       </c>
-      <c r="AE3" s="0" t="n">
+      <c r="AE3" s="1" t="n">
         <v>0.21921624417015</v>
       </c>
-      <c r="AF3" s="0" t="n">
+      <c r="AF3" s="1" t="n">
         <v>0.21921624417015</v>
       </c>
-      <c r="AO3" s="3" t="s">
+      <c r="AO3" s="4" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C4" s="3" t="n">
         <v>49881508.9255051</v>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="3" t="n">
         <v>49881508.9255051</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" s="3" t="n">
         <v>49881508.9255051</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="3" t="n">
         <v>49881508.9255051</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G4" s="3" t="n">
         <v>49881508.9255051</v>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="H4" s="3" t="n">
         <v>49881508.9255051</v>
       </c>
-      <c r="I4" s="2" t="n">
+      <c r="I4" s="3" t="n">
         <v>49881508.9255051</v>
       </c>
-      <c r="J4" s="2" t="n">
+      <c r="J4" s="3" t="n">
         <v>49881508.9255051</v>
       </c>
-      <c r="K4" s="0" t="n">
+      <c r="K4" s="1" t="n">
         <v>0.265010736793539</v>
       </c>
-      <c r="L4" s="0" t="n">
+      <c r="L4" s="1" t="n">
         <v>0.265010736793539</v>
       </c>
-      <c r="M4" s="0" t="n">
+      <c r="M4" s="1" t="n">
         <v>0.265010736793539</v>
       </c>
-      <c r="N4" s="0" t="n">
+      <c r="N4" s="1" t="n">
         <v>0.265010736793539</v>
       </c>
-      <c r="O4" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P4" s="2" t="n">
+      <c r="O4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" s="3" t="n">
         <v>21100.5360660206</v>
       </c>
-      <c r="Q4" s="2" t="n">
+      <c r="Q4" s="3" t="n">
         <v>894.898597120671</v>
       </c>
-      <c r="R4" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" s="0" t="n">
+      <c r="R4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T4" s="0" t="s">
+      <c r="T4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="U4" s="2" t="n">
+      <c r="U4" s="3" t="n">
         <v>70.3975696411597</v>
       </c>
-      <c r="V4" s="0" t="n">
+      <c r="V4" s="1" t="n">
         <v>0.175336922799585</v>
       </c>
-      <c r="W4" s="2" t="n">
-        <v>405163173.269089</v>
-      </c>
-      <c r="X4" s="2" t="n">
+      <c r="W4" s="3" t="n">
+        <v>2044812</v>
+      </c>
+      <c r="X4" s="3" t="n">
         <v>184.234184388993</v>
       </c>
-      <c r="Y4" s="0" t="s">
+      <c r="Y4" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="Z4" s="0" t="s">
+      <c r="Z4" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AA4" s="2" t="n">
+      <c r="AA4" s="3" t="n">
         <v>49881508.9255051</v>
       </c>
-      <c r="AB4" s="2" t="n">
+      <c r="AB4" s="3" t="n">
         <v>49881508.9255051</v>
       </c>
-      <c r="AC4" s="0" t="n">
+      <c r="AC4" s="1" t="n">
         <v>0.265010736793539</v>
       </c>
-      <c r="AD4" s="0" t="n">
+      <c r="AD4" s="1" t="n">
         <v>0.265010736793539</v>
       </c>
-      <c r="AE4" s="0" t="n">
+      <c r="AE4" s="1" t="n">
         <v>0.265010736793539</v>
       </c>
-      <c r="AF4" s="0" t="n">
+      <c r="AF4" s="1" t="n">
         <v>0.265010736793539</v>
       </c>
-      <c r="AO4" s="3" t="s">
+      <c r="AO4" s="4" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="C5" s="3" t="n">
         <v>62797078.6240415</v>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="3" t="n">
         <v>62797078.6240415</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" s="3" t="n">
         <v>62797078.6240415</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F5" s="3" t="n">
         <v>62797078.6240415</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="G5" s="3" t="n">
         <v>62797078.6240415</v>
       </c>
-      <c r="H5" s="2" t="n">
+      <c r="H5" s="3" t="n">
         <v>62797078.6240415</v>
       </c>
-      <c r="I5" s="2" t="n">
+      <c r="I5" s="3" t="n">
         <v>62797078.6240415</v>
       </c>
-      <c r="J5" s="2" t="n">
+      <c r="J5" s="3" t="n">
         <v>62797078.6240415</v>
       </c>
-      <c r="K5" s="0" t="n">
+      <c r="K5" s="1" t="n">
         <v>0.320371744720445</v>
       </c>
-      <c r="L5" s="0" t="n">
+      <c r="L5" s="1" t="n">
         <v>0.320371744720445</v>
       </c>
-      <c r="M5" s="0" t="n">
+      <c r="M5" s="1" t="n">
         <v>0.320371744720445</v>
       </c>
-      <c r="N5" s="0" t="n">
+      <c r="N5" s="1" t="n">
         <v>0.320371744720445</v>
       </c>
-      <c r="O5" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P5" s="2" t="n">
+      <c r="O5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" s="3" t="n">
         <v>40428.183991238</v>
       </c>
-      <c r="Q5" s="2" t="n">
+      <c r="Q5" s="3" t="n">
         <v>1223.70223967475</v>
       </c>
-      <c r="R5" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" s="0" t="n">
+      <c r="R5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T5" s="0" t="s">
+      <c r="T5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="U5" s="2" t="n">
+      <c r="U5" s="3" t="n">
         <v>81.7220746814848</v>
       </c>
-      <c r="V5" s="0" t="n">
+      <c r="V5" s="1" t="n">
         <v>0.211428976336343</v>
       </c>
-      <c r="W5" s="2" t="n">
-        <v>475911956.258991</v>
-      </c>
-      <c r="X5" s="2" t="n">
+      <c r="W5" s="3" t="n">
+        <v>2924018</v>
+      </c>
+      <c r="X5" s="3" t="n">
         <v>248.584016168097</v>
       </c>
-      <c r="Y5" s="0" t="s">
+      <c r="Y5" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="Z5" s="0" t="s">
+      <c r="Z5" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="AA5" s="2" t="n">
+      <c r="AA5" s="3" t="n">
         <v>62797078.6240415</v>
       </c>
-      <c r="AB5" s="2" t="n">
+      <c r="AB5" s="3" t="n">
         <v>62797078.6240415</v>
       </c>
-      <c r="AC5" s="0" t="n">
+      <c r="AC5" s="1" t="n">
         <v>0.320371744720445</v>
       </c>
-      <c r="AD5" s="0" t="n">
+      <c r="AD5" s="1" t="n">
         <v>0.320371744720445</v>
       </c>
-      <c r="AE5" s="0" t="n">
+      <c r="AE5" s="1" t="n">
         <v>0.320371744720445</v>
       </c>
-      <c r="AF5" s="0" t="n">
+      <c r="AF5" s="1" t="n">
         <v>0.320371744720445</v>
       </c>
-      <c r="AO5" s="3" t="s">
+      <c r="AO5" s="4" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C6" s="3" t="n">
         <v>79056812.2067715</v>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" s="3" t="n">
         <v>79056812.2067715</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" s="3" t="n">
         <v>79056812.2067715</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F6" s="3" t="n">
         <v>79056812.2067715</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="G6" s="3" t="n">
         <v>79056812.2067715</v>
       </c>
-      <c r="H6" s="2" t="n">
+      <c r="H6" s="3" t="n">
         <v>79056812.2067715</v>
       </c>
-      <c r="I6" s="2" t="n">
+      <c r="I6" s="3" t="n">
         <v>79056812.2067715</v>
       </c>
-      <c r="J6" s="2" t="n">
+      <c r="J6" s="3" t="n">
         <v>79056812.2067715</v>
       </c>
-      <c r="K6" s="0" t="n">
+      <c r="K6" s="1" t="n">
         <v>0.387297722564291</v>
       </c>
-      <c r="L6" s="0" t="n">
+      <c r="L6" s="1" t="n">
         <v>0.387297722564291</v>
       </c>
-      <c r="M6" s="0" t="n">
+      <c r="M6" s="1" t="n">
         <v>0.387297722564291</v>
       </c>
-      <c r="N6" s="0" t="n">
+      <c r="N6" s="1" t="n">
         <v>0.387297722564291</v>
       </c>
-      <c r="O6" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P6" s="2" t="n">
+      <c r="O6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" s="3" t="n">
         <v>77459.5515353483</v>
       </c>
-      <c r="Q6" s="2" t="n">
+      <c r="Q6" s="3" t="n">
         <v>1673.31491657604</v>
       </c>
-      <c r="R6" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" s="0" t="n">
+      <c r="R6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T6" s="0" t="s">
+      <c r="T6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="U6" s="2" t="n">
+      <c r="U6" s="3" t="n">
         <v>94.8682962251219</v>
       </c>
-      <c r="V6" s="0" t="n">
+      <c r="V6" s="1" t="n">
         <v>0.254950362541321</v>
       </c>
-      <c r="W6" s="2" t="n">
-        <v>559014750.237023</v>
-      </c>
-      <c r="X6" s="2" t="n">
+      <c r="W6" s="3" t="n">
+        <v>4181255</v>
+      </c>
+      <c r="X6" s="3" t="n">
         <v>335.410137370535</v>
       </c>
-      <c r="Y6" s="0" t="s">
+      <c r="Y6" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="Z6" s="0" t="s">
+      <c r="Z6" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="AA6" s="2" t="n">
+      <c r="AA6" s="3" t="n">
         <v>79056812.2067715</v>
       </c>
-      <c r="AB6" s="2" t="n">
+      <c r="AB6" s="3" t="n">
         <v>79056812.2067715</v>
       </c>
-      <c r="AC6" s="0" t="n">
+      <c r="AC6" s="1" t="n">
         <v>0.387297722564291</v>
       </c>
-      <c r="AD6" s="0" t="n">
+      <c r="AD6" s="1" t="n">
         <v>0.387297722564291</v>
       </c>
-      <c r="AE6" s="0" t="n">
+      <c r="AE6" s="1" t="n">
         <v>0.387297722564291</v>
       </c>
-      <c r="AF6" s="0" t="n">
+      <c r="AF6" s="1" t="n">
         <v>0.387297722564291</v>
       </c>
-      <c r="AO6" s="3" t="s">
+      <c r="AO6" s="4" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="C7" s="3" t="n">
         <v>99526597.3074098</v>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" s="3" t="n">
         <v>99526597.3074098</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" s="3" t="n">
         <v>99526597.3074098</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="F7" s="3" t="n">
         <v>99526597.3074098</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="G7" s="3" t="n">
         <v>99526597.3074098</v>
       </c>
-      <c r="H7" s="2" t="n">
+      <c r="H7" s="3" t="n">
         <v>99526597.3074098</v>
       </c>
-      <c r="I7" s="2" t="n">
+      <c r="I7" s="3" t="n">
         <v>99526597.3074098</v>
       </c>
-      <c r="J7" s="2" t="n">
+      <c r="J7" s="3" t="n">
         <v>99526597.3074098</v>
       </c>
-      <c r="K7" s="0" t="n">
+      <c r="K7" s="1" t="n">
         <v>0.468204604105694</v>
       </c>
-      <c r="L7" s="0" t="n">
+      <c r="L7" s="1" t="n">
         <v>0.468204604105694</v>
       </c>
-      <c r="M7" s="0" t="n">
+      <c r="M7" s="1" t="n">
         <v>0.468204604105694</v>
       </c>
-      <c r="N7" s="0" t="n">
+      <c r="N7" s="1" t="n">
         <v>0.468204604105694</v>
       </c>
-      <c r="O7" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P7" s="2" t="n">
+      <c r="O7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" s="3" t="n">
         <v>148410.874091145</v>
       </c>
-      <c r="Q7" s="2" t="n">
+      <c r="Q7" s="3" t="n">
         <v>2288.12428322441</v>
       </c>
-      <c r="R7" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" s="0" t="n">
+      <c r="R7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T7" s="0" t="s">
+      <c r="T7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="U7" s="2" t="n">
+      <c r="U7" s="3" t="n">
         <v>110.129284697376</v>
       </c>
-      <c r="V7" s="0" t="n">
+      <c r="V7" s="1" t="n">
         <v>0.307430364968277</v>
       </c>
-      <c r="W7" s="2" t="n">
-        <v>656628787.893912</v>
-      </c>
-      <c r="X7" s="2" t="n">
+      <c r="W7" s="3" t="n">
+        <v>5979066</v>
+      </c>
+      <c r="X7" s="3" t="n">
         <v>452.5631292997</v>
       </c>
-      <c r="Y7" s="0" t="s">
+      <c r="Y7" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="Z7" s="0" t="s">
+      <c r="Z7" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="AA7" s="2" t="n">
+      <c r="AA7" s="3" t="n">
         <v>99526597.3074098</v>
       </c>
-      <c r="AB7" s="2" t="n">
+      <c r="AB7" s="3" t="n">
         <v>99526597.3074098</v>
       </c>
-      <c r="AC7" s="0" t="n">
+      <c r="AC7" s="1" t="n">
         <v>0.468204604105694</v>
       </c>
-      <c r="AD7" s="0" t="n">
+      <c r="AD7" s="1" t="n">
         <v>0.468204604105694</v>
       </c>
-      <c r="AE7" s="0" t="n">
+      <c r="AE7" s="1" t="n">
         <v>0.468204604105694</v>
       </c>
-      <c r="AF7" s="0" t="n">
+      <c r="AF7" s="1" t="n">
         <v>0.468204604105694</v>
       </c>
-      <c r="AO7" s="3" t="s">
+      <c r="AO7" s="4" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C8" s="2" t="n">
+      <c r="C8" s="3" t="n">
         <v>125296521.515231</v>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" s="3" t="n">
         <v>125296521.515231</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" s="3" t="n">
         <v>125296521.515231</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F8" s="3" t="n">
         <v>125296521.515231</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="G8" s="3" t="n">
         <v>125296521.515231</v>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="H8" s="3" t="n">
         <v>125296521.515231</v>
       </c>
-      <c r="I8" s="2" t="n">
+      <c r="I8" s="3" t="n">
         <v>125296521.515231</v>
       </c>
-      <c r="J8" s="2" t="n">
+      <c r="J8" s="3" t="n">
         <v>125296521.515231</v>
       </c>
-      <c r="K8" s="0" t="n">
+      <c r="K8" s="1" t="n">
         <v>0.566013014107978</v>
       </c>
-      <c r="L8" s="0" t="n">
+      <c r="L8" s="1" t="n">
         <v>0.566013014107978</v>
       </c>
-      <c r="M8" s="0" t="n">
+      <c r="M8" s="1" t="n">
         <v>0.566013014107978</v>
       </c>
-      <c r="N8" s="0" t="n">
+      <c r="N8" s="1" t="n">
         <v>0.566013014107978</v>
       </c>
-      <c r="O8" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P8" s="2" t="n">
+      <c r="O8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" s="3" t="n">
         <v>284352.118130278</v>
       </c>
-      <c r="Q8" s="2" t="n">
+      <c r="Q8" s="3" t="n">
         <v>3128.82690736673</v>
       </c>
-      <c r="R8" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" s="0" t="n">
+      <c r="R8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T8" s="0" t="s">
+      <c r="T8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="U8" s="2" t="n">
+      <c r="U8" s="3" t="n">
         <v>127.84523208022</v>
       </c>
-      <c r="V8" s="0" t="n">
+      <c r="V8" s="1" t="n">
         <v>0.370713061014807</v>
       </c>
-      <c r="W8" s="2" t="n">
-        <v>771287993.578371</v>
-      </c>
-      <c r="X8" s="2" t="n">
+      <c r="W8" s="3" t="n">
+        <v>8549880</v>
+      </c>
+      <c r="X8" s="3" t="n">
         <v>610.635646278261</v>
       </c>
-      <c r="Y8" s="0" t="s">
+      <c r="Y8" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="Z8" s="0" t="s">
+      <c r="Z8" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="AA8" s="2" t="n">
+      <c r="AA8" s="3" t="n">
         <v>125296521.515231</v>
       </c>
-      <c r="AB8" s="2" t="n">
+      <c r="AB8" s="3" t="n">
         <v>125296521.515231</v>
       </c>
-      <c r="AC8" s="0" t="n">
+      <c r="AC8" s="1" t="n">
         <v>0.566013014107978</v>
       </c>
-      <c r="AD8" s="0" t="n">
+      <c r="AD8" s="1" t="n">
         <v>0.566013014107978</v>
       </c>
-      <c r="AE8" s="0" t="n">
+      <c r="AE8" s="1" t="n">
         <v>0.566013014107978</v>
       </c>
-      <c r="AF8" s="0" t="n">
+      <c r="AF8" s="1" t="n">
         <v>0.566013014107978</v>
       </c>
-      <c r="AM8" s="3" t="s">
+      <c r="AM8" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="AN8" s="3" t="n">
+      <c r="AN8" s="4" t="n">
         <v>0.2</v>
       </c>
-      <c r="AO8" s="3" t="s">
+      <c r="AO8" s="4" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C9" s="2" t="n">
+      <c r="C9" s="3" t="n">
         <v>157738923.348562</v>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D9" s="3" t="n">
         <v>157738923.348562</v>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" s="3" t="n">
         <v>157738923.348562</v>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="F9" s="3" t="n">
         <v>157738923.348562</v>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="G9" s="3" t="n">
         <v>157738923.348562</v>
       </c>
-      <c r="H9" s="2" t="n">
+      <c r="H9" s="3" t="n">
         <v>157738923.348562</v>
       </c>
-      <c r="I9" s="2" t="n">
+      <c r="I9" s="3" t="n">
         <v>157738923.348562</v>
       </c>
-      <c r="J9" s="2" t="n">
+      <c r="J9" s="3" t="n">
         <v>157738923.348562</v>
       </c>
-      <c r="K9" s="0" t="n">
+      <c r="K9" s="1" t="n">
         <v>0.684253698768149</v>
       </c>
-      <c r="L9" s="0" t="n">
+      <c r="L9" s="1" t="n">
         <v>0.684253698768149</v>
       </c>
-      <c r="M9" s="0" t="n">
+      <c r="M9" s="1" t="n">
         <v>0.684253698768149</v>
       </c>
-      <c r="N9" s="0" t="n">
+      <c r="N9" s="1" t="n">
         <v>0.684253698768149</v>
       </c>
-      <c r="O9" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P9" s="2" t="n">
+      <c r="O9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" s="3" t="n">
         <v>544812.686943132</v>
       </c>
-      <c r="Q9" s="2" t="n">
+      <c r="Q9" s="3" t="n">
         <v>4278.42048967141</v>
       </c>
-      <c r="R9" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" s="0" t="n">
+      <c r="R9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T9" s="0" t="s">
+      <c r="T9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="U9" s="2" t="n">
+      <c r="U9" s="3" t="n">
         <v>148.411055338804</v>
       </c>
-      <c r="V9" s="0" t="n">
+      <c r="V9" s="1" t="n">
         <v>0.447022120346339</v>
       </c>
-      <c r="W9" s="2" t="n">
-        <v>905968760.441039</v>
-      </c>
-      <c r="X9" s="2" t="n">
+      <c r="W9" s="3" t="n">
+        <v>12226064</v>
+      </c>
+      <c r="X9" s="3" t="n">
         <v>823.920174590142</v>
       </c>
-      <c r="Y9" s="0" t="s">
+      <c r="Y9" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="Z9" s="0" t="s">
+      <c r="Z9" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="AA9" s="2" t="n">
+      <c r="AA9" s="3" t="n">
         <v>157738923.348562</v>
       </c>
-      <c r="AB9" s="2" t="n">
+      <c r="AB9" s="3" t="n">
         <v>157738923.348562</v>
       </c>
-      <c r="AC9" s="0" t="n">
+      <c r="AC9" s="1" t="n">
         <v>0.684253698768149</v>
       </c>
-      <c r="AD9" s="0" t="n">
+      <c r="AD9" s="1" t="n">
         <v>0.684253698768149</v>
       </c>
-      <c r="AE9" s="0" t="n">
+      <c r="AE9" s="1" t="n">
         <v>0.684253698768149</v>
       </c>
-      <c r="AF9" s="0" t="n">
+      <c r="AF9" s="1" t="n">
         <v>0.684253698768149</v>
       </c>
-      <c r="AO9" s="3" t="s">
+      <c r="AO9" s="4" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C10" s="2" t="n">
+      <c r="C10" s="3" t="n">
         <v>198581474.076588</v>
       </c>
-      <c r="D10" s="2" t="n">
+      <c r="D10" s="3" t="n">
         <v>198581474.076588</v>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E10" s="3" t="n">
         <v>198581474.076588</v>
       </c>
-      <c r="F10" s="2" t="n">
+      <c r="F10" s="3" t="n">
         <v>198581474.076588</v>
       </c>
-      <c r="G10" s="2" t="n">
+      <c r="G10" s="3" t="n">
         <v>198581474.076588</v>
       </c>
-      <c r="H10" s="2" t="n">
+      <c r="H10" s="3" t="n">
         <v>198581474.076588</v>
       </c>
-      <c r="I10" s="2" t="n">
+      <c r="I10" s="3" t="n">
         <v>198581474.076588</v>
       </c>
-      <c r="J10" s="2" t="n">
+      <c r="J10" s="3" t="n">
         <v>198581474.076588</v>
       </c>
-      <c r="K10" s="0" t="n">
+      <c r="K10" s="1" t="n">
         <v>0.827194980694514</v>
       </c>
-      <c r="L10" s="0" t="n">
+      <c r="L10" s="1" t="n">
         <v>0.827194980694514</v>
       </c>
-      <c r="M10" s="0" t="n">
+      <c r="M10" s="1" t="n">
         <v>0.827194980694514</v>
       </c>
-      <c r="N10" s="0" t="n">
+      <c r="N10" s="1" t="n">
         <v>0.827194980694514</v>
       </c>
-      <c r="O10" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P10" s="2" t="n">
+      <c r="O10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" s="3" t="n">
         <v>1043849.66711662</v>
       </c>
-      <c r="Q10" s="2" t="n">
+      <c r="Q10" s="3" t="n">
         <v>5850.39774598648</v>
       </c>
-      <c r="R10" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" s="0" t="n">
+      <c r="R10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T10" s="0" t="s">
+      <c r="T10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="U10" s="2" t="n">
+      <c r="U10" s="3" t="n">
         <v>172.285199755881</v>
       </c>
-      <c r="V10" s="0" t="n">
+      <c r="V10" s="1" t="n">
         <v>0.53903894168691</v>
       </c>
-      <c r="W10" s="2" t="n">
-        <v>1064167213.45173</v>
-      </c>
-      <c r="X10" s="2" t="n">
+      <c r="W10" s="3" t="n">
+        <v>17482895</v>
+      </c>
+      <c r="X10" s="3" t="n">
         <v>1111.70132014748</v>
       </c>
-      <c r="Y10" s="0" t="s">
+      <c r="Y10" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="Z10" s="0" t="s">
+      <c r="Z10" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="AA10" s="2" t="n">
+      <c r="AA10" s="3" t="n">
         <v>198581474.076588</v>
       </c>
-      <c r="AB10" s="2" t="n">
+      <c r="AB10" s="3" t="n">
         <v>198581474.076588</v>
       </c>
-      <c r="AC10" s="0" t="n">
+      <c r="AC10" s="1" t="n">
         <v>0.827194980694514</v>
       </c>
-      <c r="AD10" s="0" t="n">
+      <c r="AD10" s="1" t="n">
         <v>0.827194980694514</v>
       </c>
-      <c r="AE10" s="0" t="n">
+      <c r="AE10" s="1" t="n">
         <v>0.827194980694514</v>
       </c>
-      <c r="AF10" s="0" t="n">
+      <c r="AF10" s="1" t="n">
         <v>0.827194980694514</v>
       </c>
-      <c r="AO10" s="3" t="s">
+      <c r="AO10" s="4" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C11" s="2" t="n">
+      <c r="C11" s="3" t="n">
         <v>250000000</v>
       </c>
-      <c r="D11" s="2" t="n">
+      <c r="D11" s="3" t="n">
         <v>250000000</v>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="E11" s="3" t="n">
         <v>250000000</v>
       </c>
-      <c r="F11" s="2" t="n">
+      <c r="F11" s="3" t="n">
         <v>250000000</v>
       </c>
-      <c r="G11" s="2" t="n">
+      <c r="G11" s="3" t="n">
         <v>250000000</v>
       </c>
-      <c r="H11" s="2" t="n">
+      <c r="H11" s="3" t="n">
         <v>250000000</v>
       </c>
-      <c r="I11" s="2" t="n">
+      <c r="I11" s="3" t="n">
         <v>250000000</v>
       </c>
-      <c r="J11" s="2" t="n">
+      <c r="J11" s="3" t="n">
         <v>250000000</v>
       </c>
-      <c r="K11" s="0" t="n">
+      <c r="K11" s="1" t="n">
         <v>0.999996839356578</v>
       </c>
-      <c r="L11" s="0" t="n">
+      <c r="L11" s="1" t="n">
         <v>0.999996839356578</v>
       </c>
-      <c r="M11" s="0" t="n">
+      <c r="M11" s="1" t="n">
         <v>0.999996839356578</v>
       </c>
-      <c r="N11" s="0" t="n">
+      <c r="N11" s="1" t="n">
         <v>0.999996839356578</v>
       </c>
-      <c r="O11" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P11" s="2" t="n">
+      <c r="O11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P11" s="3" t="n">
         <v>2000000</v>
       </c>
-      <c r="Q11" s="2" t="n">
+      <c r="Q11" s="3" t="n">
         <v>7999.95088581684</v>
       </c>
-      <c r="R11" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" s="0" t="n">
+      <c r="R11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T11" s="0" t="s">
+      <c r="T11" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="U11" s="2" t="n">
+      <c r="U11" s="3" t="n">
         <v>199.999858414611</v>
       </c>
-      <c r="V11" s="0" t="n">
+      <c r="V11" s="1" t="n">
         <v>0.64999687359951</v>
       </c>
-      <c r="W11" s="2" t="n">
-        <v>1249989963.93025</v>
-      </c>
-      <c r="X11" s="2" t="n">
+      <c r="W11" s="3" t="n">
+        <v>25000000</v>
+      </c>
+      <c r="X11" s="3" t="n">
         <v>1499.99947001228</v>
       </c>
-      <c r="Y11" s="0" t="s">
+      <c r="Y11" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="Z11" s="0" t="s">
+      <c r="Z11" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="AA11" s="2" t="n">
+      <c r="AA11" s="3" t="n">
         <v>250000000</v>
       </c>
-      <c r="AB11" s="2" t="n">
+      <c r="AB11" s="3" t="n">
         <v>250000000</v>
       </c>
-      <c r="AC11" s="0" t="n">
+      <c r="AC11" s="1" t="n">
         <v>0.999996839356578</v>
       </c>
-      <c r="AD11" s="0" t="n">
+      <c r="AD11" s="1" t="n">
         <v>0.999996839356578</v>
       </c>
-      <c r="AE11" s="0" t="n">
+      <c r="AE11" s="1" t="n">
         <v>0.999996839356578</v>
       </c>
-      <c r="AF11" s="0" t="n">
+      <c r="AF11" s="1" t="n">
         <v>0.999996839356578</v>
       </c>
     </row>
